--- a/5/search/FY2_Missile2_results/best_solution.xlsx
+++ b/5/search/FY2_Missile2_results/best_solution.xlsx
@@ -487,37 +487,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>279</v>
+        <v>225</v>
       </c>
       <c r="B2" t="n">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>12087.60330042253</v>
+        <v>11423.00086655178</v>
       </c>
       <c r="F2" t="n">
-        <v>846.8945292667229</v>
+        <v>823.0008665517772</v>
       </c>
       <c r="G2" t="n">
         <v>1400</v>
       </c>
       <c r="H2" t="n">
-        <v>12153.30577573943</v>
+        <v>10990.25151646561</v>
       </c>
       <c r="I2" t="n">
-        <v>432.065426216765</v>
+        <v>390.2515164656102</v>
       </c>
       <c r="J2" t="n">
-        <v>1355.9</v>
+        <v>1223.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
